--- a/Team-Data/2008-09/3-12-2008-09.xlsx
+++ b/Team-Data/2008-09/3-12-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -814,7 +881,7 @@
         <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
         <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>0.75</v>
+        <v>0.754</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
@@ -864,7 +931,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.487</v>
+        <v>0.486</v>
       </c>
       <c r="L3" t="n">
         <v>6.5</v>
@@ -873,55 +940,55 @@
         <v>16.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.394</v>
+        <v>0.392</v>
       </c>
       <c r="O3" t="n">
         <v>20.1</v>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.774</v>
+        <v>0.77</v>
       </c>
       <c r="R3" t="n">
         <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T3" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W3" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AA3" t="n">
         <v>22.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.5</v>
+        <v>101.3</v>
       </c>
       <c r="AC3" t="n">
         <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -951,16 +1018,16 @@
         <v>21</v>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="n">
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
         <v>18</v>
@@ -972,7 +1039,7 @@
         <v>8</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
         <v>27</v>
@@ -981,7 +1048,7 @@
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1170,19 @@
         <v>-1.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
         <v>17</v>
       </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1172,7 +1239,7 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="n">
         <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>0.438</v>
+        <v>0.446</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
@@ -1225,43 +1292,43 @@
         <v>37.5</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L5" t="n">
         <v>5.9</v>
       </c>
       <c r="M5" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="N5" t="n">
         <v>0.38</v>
       </c>
       <c r="O5" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.792</v>
+        <v>0.791</v>
       </c>
       <c r="R5" t="n">
         <v>12.2</v>
       </c>
       <c r="S5" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T5" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V5" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W5" t="n">
         <v>7.6</v>
@@ -1270,22 +1337,22 @@
         <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" t="n">
         <v>21.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.8</v>
+        <v>-1.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1303,7 +1370,7 @@
         <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK5" t="n">
         <v>22</v>
@@ -1318,10 +1385,10 @@
         <v>7</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1339,7 +1406,7 @@
         <v>14</v>
       </c>
       <c r="AV5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW5" t="n">
         <v>9</v>
@@ -1354,13 +1421,13 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
         <v>11</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -1392,112 +1459,112 @@
         <v>63</v>
       </c>
       <c r="E6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.794</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J6" t="n">
-        <v>78.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.469</v>
+        <v>0.468</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.394</v>
+        <v>0.389</v>
       </c>
       <c r="O6" t="n">
         <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.756</v>
+        <v>0.754</v>
       </c>
       <c r="R6" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S6" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
         <v>7.6</v>
       </c>
       <c r="X6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.2</v>
+        <v>99.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>25</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
         <v>5</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO6" t="n">
         <v>19</v>
@@ -1506,7 +1573,7 @@
         <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR6" t="n">
         <v>17</v>
@@ -1518,7 +1585,7 @@
         <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV6" t="n">
         <v>7</v>
@@ -1530,16 +1597,16 @@
         <v>6</v>
       </c>
       <c r="AY6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6</v>
       </c>
       <c r="BA6" t="n">
         <v>21</v>
       </c>
       <c r="BB6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1712,7 +1779,7 @@
         <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
         <v>3</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -1846,13 +1913,13 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ8" t="n">
         <v>23</v>
       </c>
       <c r="AK8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL8" t="n">
         <v>19</v>
@@ -1861,7 +1928,7 @@
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO8" t="n">
         <v>2</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR8" t="n">
         <v>16</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2086,7 @@
         <v>15</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
         <v>15</v>
@@ -2061,7 +2128,7 @@
         <v>17</v>
       </c>
       <c r="AT9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU9" t="n">
         <v>18</v>
@@ -2073,7 +2140,7 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY9" t="n">
         <v>5</v>
@@ -2088,7 +2155,7 @@
         <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2219,7 +2286,7 @@
         <v>13</v>
       </c>
       <c r="AL10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM10" t="n">
         <v>17</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -2377,13 +2444,13 @@
         <v>3.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG11" t="n">
         <v>6</v>
@@ -2404,7 +2471,7 @@
         <v>7</v>
       </c>
       <c r="AM11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN11" t="n">
         <v>13</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>-1.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
@@ -2583,7 +2650,7 @@
         <v>19</v>
       </c>
       <c r="AL12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM12" t="n">
         <v>3</v>
@@ -2604,7 +2671,7 @@
         <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
         <v>2</v>
@@ -2634,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2786,7 +2853,7 @@
         <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -2860,13 +2927,13 @@
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="J14" t="n">
-        <v>85.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L14" t="n">
         <v>6.8</v>
@@ -2875,25 +2942,25 @@
         <v>18.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.361</v>
+        <v>0.363</v>
       </c>
       <c r="O14" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="P14" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R14" t="n">
         <v>12.6</v>
       </c>
       <c r="S14" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
-        <v>44.1</v>
+        <v>44.3</v>
       </c>
       <c r="U14" t="n">
         <v>23.5</v>
@@ -2911,31 +2978,31 @@
         <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.5</v>
+        <v>108.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2953,16 +3020,16 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="n">
         <v>8</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
@@ -2983,13 +3050,13 @@
         <v>2</v>
       </c>
       <c r="AX14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA14" t="n">
         <v>7</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3208,7 @@
         <v>16</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
         <v>24</v>
@@ -3159,7 +3226,7 @@
         <v>30</v>
       </c>
       <c r="AV15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW15" t="n">
         <v>11</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>13</v>
@@ -3332,7 +3399,7 @@
         <v>24</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
         <v>28</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" t="n">
         <v>30</v>
       </c>
       <c r="F17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>0.455</v>
+        <v>0.448</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3412,40 +3479,40 @@
         <v>82.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L17" t="n">
         <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O17" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="P17" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R17" t="n">
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U17" t="n">
         <v>21.7</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
         <v>7.4</v>
@@ -3457,16 +3524,16 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,7 +3542,7 @@
         <v>17</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
@@ -3490,7 +3557,7 @@
         <v>8</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
@@ -3502,10 +3569,10 @@
         <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -3514,10 +3581,10 @@
         <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AU17" t="n">
         <v>9</v>
@@ -3526,13 +3593,13 @@
         <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3541,10 +3608,10 @@
         <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3669,7 +3736,7 @@
         <v>12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK18" t="n">
         <v>29</v>
@@ -3690,7 +3757,7 @@
         <v>17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR18" t="n">
         <v>5</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -3833,16 +3900,16 @@
         <v>-2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
         <v>7</v>
@@ -3893,7 +3960,7 @@
         <v>18</v>
       </c>
       <c r="AX19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY19" t="n">
         <v>15</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4151,7 @@
         <v>9</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -4197,19 +4264,19 @@
         <v>-1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
       </c>
       <c r="AF21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG21" t="n">
         <v>22</v>
       </c>
       <c r="AH21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4263,7 +4330,7 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -4391,10 +4458,10 @@
         <v>26</v>
       </c>
       <c r="AH22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI22" t="n">
         <v>14</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>15</v>
       </c>
       <c r="AJ22" t="n">
         <v>10</v>
@@ -4412,7 +4479,7 @@
         <v>21</v>
       </c>
       <c r="AO22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP22" t="n">
         <v>10</v>
@@ -4445,7 +4512,7 @@
         <v>18</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
         <v>19</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>7.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4579,7 +4646,7 @@
         <v>24</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
         <v>10</v>
@@ -4591,10 +4658,10 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4816,7 @@
         <v>16</v>
       </c>
       <c r="AF24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG24" t="n">
         <v>16</v>
@@ -4758,7 +4825,7 @@
         <v>26</v>
       </c>
       <c r="AI24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ24" t="n">
         <v>16</v>
@@ -4779,7 +4846,7 @@
         <v>13</v>
       </c>
       <c r="AP24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4809,7 +4876,7 @@
         <v>16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -4847,52 +4914,52 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E25" t="n">
         <v>34</v>
       </c>
       <c r="F25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" t="n">
-        <v>0.523</v>
+        <v>0.531</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="J25" t="n">
         <v>80.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.502</v>
+        <v>0.501</v>
       </c>
       <c r="L25" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M25" t="n">
         <v>17.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.383</v>
+        <v>0.386</v>
       </c>
       <c r="O25" t="n">
         <v>20.3</v>
       </c>
       <c r="P25" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R25" t="n">
         <v>10.2</v>
       </c>
       <c r="S25" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T25" t="n">
         <v>41.2</v>
@@ -4916,16 +4983,16 @@
         <v>20.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB25" t="n">
         <v>107.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4937,7 +5004,7 @@
         <v>14</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>2</v>
@@ -4949,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM25" t="n">
         <v>19</v>
@@ -4958,13 +5025,13 @@
         <v>5</v>
       </c>
       <c r="AO25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP25" t="n">
         <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR25" t="n">
         <v>25</v>
@@ -4973,10 +5040,10 @@
         <v>9</v>
       </c>
       <c r="AT25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV25" t="n">
         <v>29</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E26" t="n">
         <v>40</v>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.635</v>
+        <v>0.625</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J26" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.464</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="P26" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="R26" t="n">
         <v>12.9</v>
@@ -5077,7 +5144,7 @@
         <v>28.3</v>
       </c>
       <c r="T26" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U26" t="n">
         <v>20.3</v>
@@ -5092,37 +5159,37 @@
         <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.3</v>
+        <v>99</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
         <v>9</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH26" t="n">
         <v>16</v>
       </c>
       <c r="AI26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ26" t="n">
         <v>22</v>
@@ -5140,7 +5207,7 @@
         <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP26" t="n">
         <v>18</v>
@@ -5155,7 +5222,7 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="n">
         <v>20</v>
@@ -5182,7 +5249,7 @@
         <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5310,10 +5377,10 @@
         <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM27" t="n">
         <v>14</v>
@@ -5322,7 +5389,7 @@
         <v>16</v>
       </c>
       <c r="AO27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP27" t="n">
         <v>12</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E28" t="n">
         <v>43</v>
       </c>
       <c r="F28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G28" t="n">
-        <v>0.672</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
@@ -5411,7 +5478,7 @@
         <v>37.2</v>
       </c>
       <c r="J28" t="n">
-        <v>79.7</v>
+        <v>79.8</v>
       </c>
       <c r="K28" t="n">
         <v>0.466</v>
@@ -5420,34 +5487,34 @@
         <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.398</v>
+        <v>0.394</v>
       </c>
       <c r="O28" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="P28" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.767</v>
+        <v>0.77</v>
       </c>
       <c r="R28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="S28" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T28" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U28" t="n">
         <v>21.8</v>
       </c>
       <c r="V28" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="W28" t="n">
         <v>5.8</v>
@@ -5456,22 +5523,22 @@
         <v>4.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z28" t="n">
         <v>18.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5489,10 +5556,10 @@
         <v>10</v>
       </c>
       <c r="AJ28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
         <v>4</v>
@@ -5516,10 +5583,10 @@
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
         <v>7</v>
@@ -5534,7 +5601,7 @@
         <v>23</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5546,7 +5613,7 @@
         <v>23</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -5668,10 +5735,10 @@
         <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK29" t="n">
         <v>11</v>
@@ -5686,7 +5753,7 @@
         <v>12</v>
       </c>
       <c r="AO29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP29" t="n">
         <v>28</v>
@@ -5716,7 +5783,7 @@
         <v>15</v>
       </c>
       <c r="AY29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ29" t="n">
         <v>4</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -5841,10 +5908,10 @@
         <v>7</v>
       </c>
       <c r="AF30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG30" t="n">
         <v>8</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>9</v>
       </c>
       <c r="AH30" t="n">
         <v>19</v>
@@ -5883,7 +5950,7 @@
         <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
@@ -5910,7 +5977,7 @@
         <v>6</v>
       </c>
       <c r="BC30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6105,7 @@
         <v>12</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6074,7 +6141,7 @@
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX31" t="n">
         <v>25</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-12-2008-09</t>
+          <t>2009-03-12</t>
         </is>
       </c>
     </row>
